--- a/data/trans_dic/P16A20_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,01</t>
+          <t>0,4; 1,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 11,71</t>
+          <t>6,93; 11,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,01</t>
+          <t>3,69; 5,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,45</t>
+          <t>0,39; 2,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,03</t>
+          <t>5,6; 10,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,44</t>
+          <t>3,06; 5,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 13,1</t>
+          <t>6,06; 12,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,4</t>
+          <t>0,82; 3,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,63</t>
+          <t>1,02; 2,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 59,26</t>
+          <t>8,03; 63,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 37,86</t>
+          <t>4,42; 39,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,49</t>
+          <t>0,76; 3,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,0</t>
+          <t>6,36; 11,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,64</t>
+          <t>4,83; 7,57</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,02</t>
+          <t>5,21; 8,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,85</t>
+          <t>4,11; 7,11</t>
         </is>
       </c>
     </row>
@@ -1557,17 +1557,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,72; 29,69</t>
+          <t>7,78; 31,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 17,07</t>
+          <t>4,49; 18,26</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1992</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2184; 10142</t>
+          <t>2035; 9971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2109</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1928</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30853; 52377</t>
+          <t>31006; 51472</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34798; 57264</t>
+          <t>35132; 56534</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2049</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2149</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2053</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1822; 11059</t>
+          <t>1762; 10545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2065</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21350; 38391</t>
+          <t>21414; 38473</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2126</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2030</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26137; 45406</t>
+          <t>25528; 44316</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1994</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7585</t>
+          <t>0; 8403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2030</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1908</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9694; 21872</t>
+          <t>10113; 21527</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1994</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6394; 28370</t>
+          <t>6884; 28973</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1987</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2022</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2004</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11109; 27184</t>
+          <t>10548; 27438</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2018</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2041</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79454; 579035</t>
+          <t>78458; 617546</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2031</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89025; 761705</t>
+          <t>89000; 799313</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2008</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2034</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4073; 16565</t>
+          <t>3591; 15587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2104</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1934</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52311; 92281</t>
+          <t>53400; 94006</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2036</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62528; 100357</t>
+          <t>63361; 99345</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1871</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 20039</t>
+          <t>0; 18613</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1896</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39175; 60904</t>
+          <t>39539; 63111</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1891</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41209; 68502</t>
+          <t>41093; 71112</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2031</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29209; 59059</t>
+          <t>29505; 59087</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>275972; 1060708</t>
+          <t>278111; 1126475</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 1996</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>313081; 1185963</t>
+          <t>311924; 1268785</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A20_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,97</t>
+          <t>0,42; 1,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,5</t>
+          <t>6,78; 11,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,93</t>
+          <t>3,73; 5,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,33</t>
+          <t>0,39; 2,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,06</t>
+          <t>5,89; 10,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,31</t>
+          <t>3,16; 5,36</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,16; 1,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 12,9</t>
+          <t>6,16; 12,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,47</t>
+          <t>2,05; 4,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,65</t>
+          <t>1,05; 2,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 63,2</t>
+          <t>7,22; 10,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 39,73</t>
+          <t>3,88; 5,47</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,29</t>
+          <t>0,78; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,2</t>
+          <t>7,62; 10,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,14 +1332,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,57</t>
+          <t>5,01; 7,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,31</t>
+          <t>5,19; 8,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,11</t>
+          <t>4,46; 7,03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,75</t>
+          <t>0,91; 1,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 31,53</t>
+          <t>7,52; 9,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 18,26</t>
+          <t>4,42; 5,32</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44764</t>
+          <t>49145</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2035; 9971</t>
+          <t>2316; 10837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31006; 51472</t>
+          <t>33119; 55074</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35132; 56534</t>
+          <t>38749; 62025</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>32975</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>37933</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1762; 10545</t>
+          <t>1900; 11188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21414; 38473</t>
+          <t>24935; 43491</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25528; 44316</t>
+          <t>28642; 48551</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>19497</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 8403</t>
+          <t>774; 6691</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10113; 21527</t>
+          <t>11552; 24134</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6884; 28973</t>
+          <t>13482; 27686</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>271520</t>
+          <t>74743</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>289013</t>
+          <t>92893</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10548; 27438</t>
+          <t>11883; 27339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78458; 617546</t>
+          <t>62130; 88161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89000; 799313</t>
+          <t>77252; 109066</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71968</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79925</t>
+          <t>83762</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3591; 15587</t>
+          <t>4399; 17713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53400; 94006</t>
+          <t>63274; 88721</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2814,14 +2814,14 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63361; 99345</t>
+          <t>70010; 99174</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48813</t>
+          <t>56634</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>52636</t>
+          <t>60025</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 18613</t>
+          <t>0; 17564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39539; 63111</t>
+          <t>43743; 69432</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41093; 71112</t>
+          <t>48123; 75902</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41811</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>476622</t>
+          <t>299578</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>518433</t>
+          <t>343255</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29505; 59087</t>
+          <t>31318; 58491</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>278111; 1126475</t>
+          <t>273207; 332094</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>311924; 1268785</t>
+          <t>312850; 376288</t>
         </is>
       </c>
     </row>
